--- a/submission/MOU_1_zhangsan/score.xlsx
+++ b/submission/MOU_1_zhangsan/score.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="18352" windowHeight="8055"/>
   </bookViews>
   <sheets>
     <sheet name="myCPU计算" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="71">
   <si>
     <t>队名</t>
   </si>
@@ -377,48 +377,6 @@
   </si>
   <si>
     <t>32ce13</t>
-  </si>
-  <si>
-    <t>fireye_D1</t>
-  </si>
-  <si>
-    <t>466edc</t>
-  </si>
-  <si>
-    <t>fireye_I2</t>
-  </si>
-  <si>
-    <t>481581</t>
-  </si>
-  <si>
-    <t>inner_product</t>
-  </si>
-  <si>
-    <t>167b7a3</t>
-  </si>
-  <si>
-    <t>lookup_table</t>
-  </si>
-  <si>
-    <t>692058</t>
-  </si>
-  <si>
-    <t>loop_induction</t>
-  </si>
-  <si>
-    <t>f413bb</t>
-  </si>
-  <si>
-    <t>my_memcmp</t>
-  </si>
-  <si>
-    <t>5895c9</t>
-  </si>
-  <si>
-    <t>minmax_sequence</t>
-  </si>
-  <si>
-    <t>848ec1</t>
   </si>
   <si>
     <r>
@@ -486,6 +444,48 @@
   </si>
   <si>
     <t>数码管显示</t>
+  </si>
+  <si>
+    <t>fireye_D1</t>
+  </si>
+  <si>
+    <t>466edc</t>
+  </si>
+  <si>
+    <t>fireye_I2</t>
+  </si>
+  <si>
+    <t>481581</t>
+  </si>
+  <si>
+    <t>inner_product</t>
+  </si>
+  <si>
+    <t>167b7a3</t>
+  </si>
+  <si>
+    <t>lookup_table</t>
+  </si>
+  <si>
+    <t>692058</t>
+  </si>
+  <si>
+    <t>loop_induction</t>
+  </si>
+  <si>
+    <t>f413bb</t>
+  </si>
+  <si>
+    <t>my_memcmp</t>
+  </si>
+  <si>
+    <t>5895c9</t>
+  </si>
+  <si>
+    <t>minmax_sequence</t>
+  </si>
+  <si>
+    <t>848ec1</t>
   </si>
 </sst>
 </file>
@@ -1783,18 +1783,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:M44"/>
+  <dimension ref="A2:M37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="21.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.125" style="10" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" customWidth="1"/>
-    <col min="3" max="3" width="18.75" style="10" customWidth="1"/>
-    <col min="4" max="4" width="17.75" style="10" customWidth="1"/>
+    <col min="1" max="1" width="5.12389380530973" style="10" customWidth="1"/>
+    <col min="2" max="2" width="14.2477876106195" style="10" customWidth="1"/>
+    <col min="3" max="3" width="18.7522123893805" style="10" customWidth="1"/>
+    <col min="4" max="4" width="17.7522123893805" style="10" customWidth="1"/>
     <col min="5" max="5" width="15" style="10" customWidth="1"/>
-    <col min="6" max="6" width="14.25" style="10" customWidth="1"/>
-    <col min="7" max="7" width="3.125" style="10" customWidth="1"/>
-    <col min="8" max="8" width="20.5833333333333" style="10" customWidth="1"/>
-    <col min="9" max="9" width="16.625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="14.2477876106195" style="10" customWidth="1"/>
+    <col min="7" max="7" width="3.12389380530973" style="10" customWidth="1"/>
+    <col min="8" max="8" width="20.5840707964602" style="10" customWidth="1"/>
+    <col min="9" max="9" width="16.6283185840708" style="10" customWidth="1"/>
     <col min="10" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
@@ -1926,7 +1926,7 @@
         <v>19</v>
       </c>
       <c r="I17" s="34">
-        <f>GEOMEAN(F21:F37)</f>
+        <f>GEOMEAN(F21:F30)</f>
         <v>0.1</v>
       </c>
       <c r="M17" s="35"/>
@@ -2148,200 +2148,74 @@
         <v>49</v>
       </c>
       <c r="F30" s="31">
-        <f t="shared" ref="F30:F37" si="1">IF(HEX2DEC(D30),HEX2DEC(E30)/HEX2DEC(D30),0.1)</f>
+        <f>IF(HEX2DEC(D30),HEX2DEC(E30)/HEX2DEC(D30),0.1)</f>
         <v>0.1</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="2:6">
-      <c r="B31" s="26">
-        <v>11</v>
-      </c>
-      <c r="C31" s="4" t="s">
+    <row r="32" customHeight="1" spans="1:6">
+      <c r="A32" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E31" s="6" t="s">
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:6">
+      <c r="A33" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F31" s="31">
-        <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="2:6">
-      <c r="B32" s="26">
-        <v>12</v>
-      </c>
-      <c r="C32" s="4" t="s">
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:6">
+      <c r="A34" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="6" t="s">
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:6">
+      <c r="A35" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="F32" s="31">
-        <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="2:6">
-      <c r="B33" s="26">
-        <v>13</v>
-      </c>
-      <c r="C33" s="4" t="s">
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:6">
+      <c r="A36" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D33" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E33" s="6" t="s">
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:6">
+      <c r="A37" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F33" s="31">
-        <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="2:6">
-      <c r="B34" s="26">
-        <v>14</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D34" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F34" s="31">
-        <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="2:6">
-      <c r="B35" s="26">
-        <v>15</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D35" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F35" s="31">
-        <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="2:6">
-      <c r="B36" s="26">
-        <v>16</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D36" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F36" s="31">
-        <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="2:6">
-      <c r="B37" s="26">
-        <v>17</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D37" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F37" s="31">
-        <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="1:6">
-      <c r="A39" s="19" t="s">
-        <v>64</v>
-      </c>
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:6">
-      <c r="A40" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:6">
-      <c r="A41" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="B41" s="20"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:6">
-      <c r="A42" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B42" s="20"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:6">
-      <c r="A43" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:6">
-      <c r="A44" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B44" s="20"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
     </row>
   </sheetData>
   <sheetProtection password="8E9E" sheet="1" objects="1"/>
   <protectedRanges>
-    <protectedRange sqref="C2:D3 F2:G3 C8 I18 D20:D37" name="允许修改"/>
+    <protectedRange sqref="C2:D3 F2:G3 C8 I18 D20:D30" name="允许修改"/>
   </protectedRanges>
   <mergeCells count="9">
     <mergeCell ref="C2:D2"/>
@@ -2364,7 +2238,7 @@
       <formula2>89</formula2>
     </dataValidation>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="上板频率" prompt="格式为:XX MHz : 100MHz&#10;XX MHz为myCPU上板频率，timer_clk必须为100MHz" sqref="D20"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="输入计时结果" prompt="要求为16进制数。&#10;如结果为0x144FF46，则填写144FF46。&#10;如果某一性能测试未通过，则填写0" sqref="D21:D28 D29:D37"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="输入计时结果" prompt="要求为16进制数。&#10;如结果为0x144FF46，则填写144FF46。&#10;如果某一性能测试未通过，则填写0" sqref="D21:D28 D29:D30"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -2376,11 +2250,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="15.75" defaultRowHeight="21" customHeight="1" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="15.7522123893805" defaultRowHeight="21" customHeight="1" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="9.125" customWidth="1"/>
-    <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="3" width="15.125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.12389380530973" customWidth="1"/>
+    <col min="2" max="2" width="14.5044247787611" customWidth="1"/>
+    <col min="3" max="3" width="15.1238938053097" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:3">
@@ -2398,7 +2272,7 @@
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="3" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:3">
@@ -2527,10 +2401,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
@@ -2538,10 +2412,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:3">
@@ -2549,10 +2423,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
@@ -2560,10 +2434,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
@@ -2571,10 +2445,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
@@ -2582,10 +2456,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:3">
@@ -2593,10 +2467,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
